--- a/health_coach_forms/003_wellness_survey--health_coach_forms.xlsx
+++ b/health_coach_forms/003_wellness_survey--health_coach_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -777,8 +777,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -806,12 +806,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sedentary'}</t>
+          <t>sedentary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sedentary'}</t>
+          <t>Sedentary</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Often'}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'landline'}</t>
+          <t>landline</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Landline'}</t>
+          <t>Landline</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cellphone'}</t>
+          <t>cellphone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cellphone'}</t>
+          <t>Cellphone</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
